--- a/Avancado/11 - Funções Financeiras.xlsx
+++ b/Avancado/11 - Funções Financeiras.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20730"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wilck.alunos\Desktop\EXCEL-completo\Avancado\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33ADA694-8A19-4D16-A4FC-FAE84AB24DFA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="179021"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -18,9 +24,49 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="10">
+  <si>
+    <t>Valor Presente</t>
+  </si>
+  <si>
+    <t>Valor Futuro</t>
+  </si>
+  <si>
+    <t>Prazo (meses)</t>
+  </si>
+  <si>
+    <t>Taxa</t>
+  </si>
+  <si>
+    <t>a)</t>
+  </si>
+  <si>
+    <t>b)</t>
+  </si>
+  <si>
+    <t>c)</t>
+  </si>
+  <si>
+    <t>d)</t>
+  </si>
+  <si>
+    <t>e)</t>
+  </si>
+  <si>
+    <t>PGTO</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="3">
+    <numFmt numFmtId="8" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,16 +74,43 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,15 +118,69 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentagem" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,10 +457,193 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A2:F18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" style="7" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="18.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="6">
+        <v>61850</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="6">
+        <v>77520</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="12">
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="5">
+        <v>10</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="13">
+        <f>RATE(B5, ,-B3,B4)</f>
+        <v>2.2839299226108837E-2</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="14">
+        <f>FV(E4,E5, ,-E3)</f>
+        <v>11264.925865953057</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E7" s="7"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="7"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="9">
+        <v>38000</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E9" s="10">
+        <f>PV(E10,E11,,-E12)</f>
+        <v>4682.3413449222344</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="9">
+        <v>76000</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="12">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="5">
+        <f>TRUNC(NPER(B12, , -B9,B10),0)</f>
+        <v>14</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E11" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="12">
+        <v>0.05</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" s="6">
+        <v>5000</v>
+      </c>
+      <c r="F12" s="15"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="6">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="8">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B17" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="11">
+        <f>PMT(B16,B17,-B15)</f>
+        <v>343.37142451431725</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>